--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="57">
   <si>
     <t>Id</t>
   </si>
@@ -146,7 +146,7 @@
     <t>财富契约</t>
   </si>
   <si>
-    <t>广告的金币经验收益+10%</t>
+    <t>广告的金币经验收益+10%，每10个额外+1经验丹</t>
   </si>
   <si>
     <t>天使之翼</t>
@@ -192,6 +192,12 @@
   </si>
   <si>
     <t>极·圣者遗物</t>
+  </si>
+  <si>
+    <t>极·副本契约</t>
+  </si>
+  <si>
+    <t>极·BOSS契约</t>
   </si>
 </sst>
 </file>
@@ -1157,7 +1163,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J31"/>
+  <dimension ref="C3:J33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1627,7 +1633,7 @@
         <v>10</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I20" s="1">
         <v>100</v>
@@ -1835,13 +1841,65 @@
         <v>1</v>
       </c>
       <c r="H31" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I31" s="1">
         <v>1</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:10">
+      <c r="C32" s="1">
+        <v>32</v>
+      </c>
+      <c r="D32" s="3">
+        <v>180032</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F32" s="1">
+        <v>4</v>
+      </c>
+      <c r="G32" s="1">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1">
+        <v>16</v>
+      </c>
+      <c r="I32" s="1">
+        <v>1</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:10">
+      <c r="C33" s="1">
+        <v>33</v>
+      </c>
+      <c r="D33" s="3">
+        <v>180033</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F33" s="1">
+        <v>2</v>
+      </c>
+      <c r="G33" s="1">
+        <v>1</v>
+      </c>
+      <c r="H33" s="1">
+        <v>8</v>
+      </c>
+      <c r="I33" s="1">
+        <v>1</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="59">
   <si>
     <t>Id</t>
   </si>
@@ -47,7 +47,7 @@
     <t>MaxCount</t>
   </si>
   <si>
-    <t>DropRate</t>
+    <t>Quality</t>
   </si>
   <si>
     <t>Des</t>
@@ -198,6 +198,12 @@
   </si>
   <si>
     <t>极·BOSS契约</t>
+  </si>
+  <si>
+    <t>极.财富契约</t>
+  </si>
+  <si>
+    <t>广告的金币经验收益+100%，每1个额外+1经验丹</t>
   </si>
 </sst>
 </file>
@@ -1163,7 +1169,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J33"/>
+  <dimension ref="C3:J34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1272,7 +1278,7 @@
         <v>4</v>
       </c>
       <c r="I6" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>11</v>
@@ -1298,7 +1304,7 @@
         <v>4</v>
       </c>
       <c r="I7" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>13</v>
@@ -1324,7 +1330,7 @@
         <v>780</v>
       </c>
       <c r="I8" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>15</v>
@@ -1350,7 +1356,7 @@
         <v>8</v>
       </c>
       <c r="I9" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>17</v>
@@ -1376,7 +1382,7 @@
         <v>10</v>
       </c>
       <c r="I10" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>19</v>
@@ -1402,7 +1408,7 @@
         <v>200</v>
       </c>
       <c r="I11" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>21</v>
@@ -1428,7 +1434,7 @@
         <v>2</v>
       </c>
       <c r="I12" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>23</v>
@@ -1454,7 +1460,7 @@
         <v>20</v>
       </c>
       <c r="I13" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>25</v>
@@ -1480,7 +1486,7 @@
         <v>4</v>
       </c>
       <c r="I14" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>27</v>
@@ -1506,7 +1512,7 @@
         <v>10</v>
       </c>
       <c r="I15" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>29</v>
@@ -1532,7 +1538,7 @@
         <v>200</v>
       </c>
       <c r="I16" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>31</v>
@@ -1558,7 +1564,7 @@
         <v>30</v>
       </c>
       <c r="I17" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>33</v>
@@ -1584,7 +1590,7 @@
         <v>200</v>
       </c>
       <c r="I18" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>35</v>
@@ -1610,7 +1616,7 @@
         <v>100</v>
       </c>
       <c r="I19" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>37</v>
@@ -1636,7 +1642,7 @@
         <v>200</v>
       </c>
       <c r="I20" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>39</v>
@@ -1662,7 +1668,7 @@
         <v>1</v>
       </c>
       <c r="I21" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>41</v>
@@ -1688,7 +1694,7 @@
         <v>250</v>
       </c>
       <c r="I22" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>43</v>
@@ -1714,7 +1720,7 @@
         <v>50</v>
       </c>
       <c r="I23" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>45</v>
@@ -1740,7 +1746,7 @@
         <v>5</v>
       </c>
       <c r="I24" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>47</v>
@@ -1766,7 +1772,7 @@
         <v>40</v>
       </c>
       <c r="I25" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>49</v>
@@ -1792,7 +1798,7 @@
         <v>50</v>
       </c>
       <c r="I26" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>51</v>
@@ -1818,7 +1824,7 @@
         <v>55</v>
       </c>
       <c r="I30" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>53</v>
@@ -1844,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>27</v>
@@ -1870,7 +1876,7 @@
         <v>16</v>
       </c>
       <c r="I32" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>17</v>
@@ -1896,10 +1902,36 @@
         <v>8</v>
       </c>
       <c r="I33" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:10">
+      <c r="C34" s="1">
+        <v>34</v>
+      </c>
+      <c r="D34" s="3">
+        <v>180034</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F34" s="1">
+        <v>15</v>
+      </c>
+      <c r="G34" s="1">
+        <v>100</v>
+      </c>
+      <c r="H34" s="1">
+        <v>8</v>
+      </c>
+      <c r="I34" s="1">
+        <v>7</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -1769,7 +1769,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I25" s="1">
         <v>6</v>
@@ -1870,7 +1870,7 @@
         <v>4</v>
       </c>
       <c r="G32" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H32" s="1">
         <v>16</v>
@@ -1896,7 +1896,7 @@
         <v>2</v>
       </c>
       <c r="G33" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" s="1">
         <v>8</v>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="61">
   <si>
     <t>Id</t>
   </si>
@@ -188,7 +188,7 @@
     <t>极·卖身契</t>
   </si>
   <si>
-    <t>矿工额外加1</t>
+    <t>超级矿工额外加1</t>
   </si>
   <si>
     <t>极·圣者遗物</t>
@@ -197,7 +197,13 @@
     <t>极·副本契约</t>
   </si>
   <si>
+    <t>广告的副本劵收益+3</t>
+  </si>
+  <si>
     <t>极·BOSS契约</t>
+  </si>
+  <si>
+    <t>广告的BOSS劵收益+2</t>
   </si>
   <si>
     <t>极.财富契约</t>
@@ -1841,7 +1847,7 @@
         <v>54</v>
       </c>
       <c r="F31" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -1879,7 +1885,7 @@
         <v>7</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:10">
@@ -1890,7 +1896,7 @@
         <v>180033</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F33" s="1">
         <v>2</v>
@@ -1905,7 +1911,7 @@
         <v>7</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:10">
@@ -1916,7 +1922,7 @@
         <v>180034</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F34" s="1">
         <v>15</v>
@@ -1931,7 +1937,7 @@
         <v>7</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -1879,7 +1879,7 @@
         <v>3</v>
       </c>
       <c r="H32" s="1">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I32" s="1">
         <v>7</v>
@@ -1905,7 +1905,7 @@
         <v>2</v>
       </c>
       <c r="H33" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I33" s="1">
         <v>7</v>
@@ -1931,7 +1931,7 @@
         <v>100</v>
       </c>
       <c r="H34" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I34" s="1">
         <v>7</v>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -1879,7 +1879,7 @@
         <v>3</v>
       </c>
       <c r="H32" s="1">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I32" s="1">
         <v>7</v>
@@ -1905,7 +1905,7 @@
         <v>2</v>
       </c>
       <c r="H33" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I33" s="1">
         <v>7</v>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -1697,7 +1697,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="1">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="I22" s="1">
         <v>6</v>
@@ -1723,7 +1723,7 @@
         <v>1</v>
       </c>
       <c r="H23" s="1">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="I23" s="1">
         <v>6</v>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="63">
   <si>
     <t>Id</t>
   </si>
@@ -210,6 +210,12 @@
   </si>
   <si>
     <t>广告的金币经验收益+100%，每1个额外+1经验丹</t>
+  </si>
+  <si>
+    <t>极.魔法书</t>
+  </si>
+  <si>
+    <t>极.无限之魂</t>
   </si>
 </sst>
 </file>
@@ -1175,7 +1181,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J34"/>
+  <dimension ref="C3:J36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1940,6 +1946,58 @@
         <v>60</v>
       </c>
     </row>
+    <row r="35" customHeight="1" spans="3:10">
+      <c r="C35" s="1">
+        <v>35</v>
+      </c>
+      <c r="D35" s="3">
+        <v>180035</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F35" s="1">
+        <v>8</v>
+      </c>
+      <c r="G35" s="1">
+        <v>15</v>
+      </c>
+      <c r="H35" s="1">
+        <v>10</v>
+      </c>
+      <c r="I35" s="1">
+        <v>7</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:10">
+      <c r="C36" s="1">
+        <v>36</v>
+      </c>
+      <c r="D36" s="3">
+        <v>180036</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F36" s="1">
+        <v>10</v>
+      </c>
+      <c r="G36" s="1">
+        <v>2</v>
+      </c>
+      <c r="H36" s="1">
+        <v>10</v>
+      </c>
+      <c r="I36" s="1">
+        <v>7</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="65">
   <si>
     <t>Id</t>
   </si>
@@ -215,7 +215,13 @@
     <t>极.魔法书</t>
   </si>
   <si>
+    <t>所有技能上限提高15%</t>
+  </si>
+  <si>
     <t>极.无限之魂</t>
+  </si>
+  <si>
+    <t>魂环等级上限+2</t>
   </si>
 </sst>
 </file>
@@ -1969,7 +1975,7 @@
         <v>7</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:10">
@@ -1980,7 +1986,7 @@
         <v>180036</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F36" s="1">
         <v>10</v>
@@ -1995,7 +2001,7 @@
         <v>7</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -1787,7 +1787,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="1">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I25" s="1">
         <v>6</v>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -1813,7 +1813,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="1">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="I26" s="1">
         <v>6</v>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -1423,7 +1423,7 @@
         <v>10</v>
       </c>
       <c r="H11" s="1">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I11" s="1">
         <v>6</v>
@@ -1605,7 +1605,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="1">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I18" s="1">
         <v>6</v>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -407,12 +407,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -737,7 +743,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -761,16 +767,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -779,95 +785,97 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1199,80 +1207,80 @@
   </cols>
   <sheetData>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="2" t="s">
+      <c r="I3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="D4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="I4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="3" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1280,7 +1288,7 @@
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="4">
         <v>180001</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -1306,7 +1314,7 @@
       <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="4">
         <v>180002</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -1332,7 +1340,7 @@
       <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="4">
         <v>180003</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -1358,7 +1366,7 @@
       <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="4">
         <v>180004</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -1384,7 +1392,7 @@
       <c r="C10" s="1">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="4">
         <v>180005</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -1406,29 +1414,29 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="3:10">
-      <c r="C11" s="1">
-        <v>6</v>
-      </c>
-      <c r="D11" s="3">
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C11" s="2">
+        <v>6</v>
+      </c>
+      <c r="D11" s="5">
         <v>180006</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="1">
-        <v>6</v>
-      </c>
-      <c r="G11" s="1">
+      <c r="F11" s="2">
+        <v>6</v>
+      </c>
+      <c r="G11" s="2">
         <v>10</v>
       </c>
-      <c r="H11" s="1">
-        <v>300</v>
-      </c>
-      <c r="I11" s="1">
-        <v>6</v>
-      </c>
-      <c r="J11" s="1" t="s">
+      <c r="H11" s="2">
+        <v>400</v>
+      </c>
+      <c r="I11" s="2">
+        <v>6</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1436,7 +1444,7 @@
       <c r="C12" s="1">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="4">
         <v>180007</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -1462,7 +1470,7 @@
       <c r="C13" s="1">
         <v>8</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="4">
         <v>180008</v>
       </c>
       <c r="E13" s="1" t="s">
@@ -1488,7 +1496,7 @@
       <c r="C14" s="1">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="4">
         <v>180009</v>
       </c>
       <c r="E14" s="1" t="s">
@@ -1514,7 +1522,7 @@
       <c r="C15" s="1">
         <v>10</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="4">
         <v>180010</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -1536,133 +1544,133 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="3:10">
-      <c r="C16" s="1">
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C16" s="2">
         <v>11</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="5">
         <v>180011</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="2">
         <v>11</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" s="2">
         <v>1000</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H16" s="2">
+        <v>300</v>
+      </c>
+      <c r="I16" s="2">
+        <v>6</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C17" s="2">
+        <v>12</v>
+      </c>
+      <c r="D17" s="5">
+        <v>180012</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" s="2">
+        <v>12</v>
+      </c>
+      <c r="G17" s="2">
+        <v>5</v>
+      </c>
+      <c r="H17" s="2">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2">
+        <v>6</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C18" s="2">
+        <v>13</v>
+      </c>
+      <c r="D18" s="5">
+        <v>180013</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" s="2">
+        <v>13</v>
+      </c>
+      <c r="G18" s="2">
+        <v>1</v>
+      </c>
+      <c r="H18" s="2">
+        <v>400</v>
+      </c>
+      <c r="I18" s="2">
+        <v>6</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C19" s="2">
+        <v>14</v>
+      </c>
+      <c r="D19" s="5">
+        <v>180014</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" s="2">
+        <v>14</v>
+      </c>
+      <c r="G19" s="2">
+        <v>10</v>
+      </c>
+      <c r="H19" s="2">
         <v>200</v>
       </c>
-      <c r="I16" s="1">
-        <v>6</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:10">
-      <c r="C17" s="1">
-        <v>12</v>
-      </c>
-      <c r="D17" s="3">
-        <v>180012</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F17" s="1">
-        <v>12</v>
-      </c>
-      <c r="G17" s="1">
-        <v>5</v>
-      </c>
-      <c r="H17" s="1">
-        <v>30</v>
-      </c>
-      <c r="I17" s="1">
-        <v>6</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:10">
-      <c r="C18" s="1">
-        <v>13</v>
-      </c>
-      <c r="D18" s="3">
-        <v>180013</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F18" s="1">
-        <v>13</v>
-      </c>
-      <c r="G18" s="1">
-        <v>1</v>
-      </c>
-      <c r="H18" s="1">
+      <c r="I19" s="2">
+        <v>6</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C20" s="2">
+        <v>15</v>
+      </c>
+      <c r="D20" s="5">
+        <v>180015</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" s="2">
+        <v>15</v>
+      </c>
+      <c r="G20" s="2">
+        <v>10</v>
+      </c>
+      <c r="H20" s="2">
         <v>300</v>
       </c>
-      <c r="I18" s="1">
-        <v>6</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:10">
-      <c r="C19" s="1">
-        <v>14</v>
-      </c>
-      <c r="D19" s="3">
-        <v>180014</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F19" s="1">
-        <v>14</v>
-      </c>
-      <c r="G19" s="1">
-        <v>10</v>
-      </c>
-      <c r="H19" s="1">
-        <v>100</v>
-      </c>
-      <c r="I19" s="1">
-        <v>6</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:10">
-      <c r="C20" s="1">
-        <v>15</v>
-      </c>
-      <c r="D20" s="3">
-        <v>180015</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" s="1">
-        <v>15</v>
-      </c>
-      <c r="G20" s="1">
-        <v>10</v>
-      </c>
-      <c r="H20" s="1">
-        <v>200</v>
-      </c>
-      <c r="I20" s="1">
-        <v>6</v>
-      </c>
-      <c r="J20" s="1" t="s">
+      <c r="I20" s="2">
+        <v>6</v>
+      </c>
+      <c r="J20" s="2" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1670,7 +1678,7 @@
       <c r="C21" s="1">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="4">
         <v>180016</v>
       </c>
       <c r="E21" s="1" t="s">
@@ -1692,55 +1700,55 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="3:10">
-      <c r="C22" s="1">
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C22" s="2">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="5">
         <v>180017</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22" s="2">
         <v>17</v>
       </c>
-      <c r="G22" s="1">
-        <v>1</v>
-      </c>
-      <c r="H22" s="1">
-        <v>500</v>
-      </c>
-      <c r="I22" s="1">
-        <v>6</v>
-      </c>
-      <c r="J22" s="1" t="s">
+      <c r="G22" s="2">
+        <v>1</v>
+      </c>
+      <c r="H22" s="2">
+        <v>800</v>
+      </c>
+      <c r="I22" s="2">
+        <v>6</v>
+      </c>
+      <c r="J22" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="3:10">
-      <c r="C23" s="1">
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C23" s="2">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="5">
         <v>180018</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="2">
         <v>18</v>
       </c>
-      <c r="G23" s="1">
-        <v>1</v>
-      </c>
-      <c r="H23" s="1">
-        <v>70</v>
-      </c>
-      <c r="I23" s="1">
-        <v>6</v>
-      </c>
-      <c r="J23" s="1" t="s">
+      <c r="G23" s="2">
+        <v>1</v>
+      </c>
+      <c r="H23" s="2">
+        <v>100</v>
+      </c>
+      <c r="I23" s="2">
+        <v>6</v>
+      </c>
+      <c r="J23" s="2" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1748,7 +1756,7 @@
       <c r="C24" s="1">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="4">
         <v>180019</v>
       </c>
       <c r="E24" s="1" t="s">
@@ -1770,55 +1778,55 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="3:10">
-      <c r="C25" s="1">
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C25" s="2">
         <v>20</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="5">
         <v>180020</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25" s="2">
         <v>20</v>
       </c>
-      <c r="G25" s="1">
-        <v>1</v>
-      </c>
-      <c r="H25" s="1">
-        <v>80</v>
-      </c>
-      <c r="I25" s="1">
-        <v>6</v>
-      </c>
-      <c r="J25" s="1" t="s">
+      <c r="G25" s="2">
+        <v>1</v>
+      </c>
+      <c r="H25" s="2">
+        <v>100</v>
+      </c>
+      <c r="I25" s="2">
+        <v>6</v>
+      </c>
+      <c r="J25" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="3:10">
-      <c r="C26" s="1">
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C26" s="2">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="5">
         <v>180021</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26" s="2">
         <v>21</v>
       </c>
-      <c r="G26" s="1">
-        <v>1</v>
-      </c>
-      <c r="H26" s="1">
-        <v>80</v>
-      </c>
-      <c r="I26" s="1">
-        <v>6</v>
-      </c>
-      <c r="J26" s="1" t="s">
+      <c r="G26" s="2">
+        <v>1</v>
+      </c>
+      <c r="H26" s="2">
+        <v>100</v>
+      </c>
+      <c r="I26" s="2">
+        <v>6</v>
+      </c>
+      <c r="J26" s="2" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1826,7 +1834,7 @@
       <c r="C30" s="1">
         <v>30</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D30" s="4">
         <v>180030</v>
       </c>
       <c r="E30" s="1" t="s">
@@ -1839,7 +1847,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="1">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="I30" s="1">
         <v>7</v>
@@ -1852,7 +1860,7 @@
       <c r="C31" s="1">
         <v>31</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D31" s="4">
         <v>180031</v>
       </c>
       <c r="E31" s="1" t="s">
@@ -1878,7 +1886,7 @@
       <c r="C32" s="1">
         <v>32</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="4">
         <v>180032</v>
       </c>
       <c r="E32" s="1" t="s">
@@ -1904,7 +1912,7 @@
       <c r="C33" s="1">
         <v>33</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="4">
         <v>180033</v>
       </c>
       <c r="E33" s="1" t="s">
@@ -1930,7 +1938,7 @@
       <c r="C34" s="1">
         <v>34</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D34" s="4">
         <v>180034</v>
       </c>
       <c r="E34" s="1" t="s">
@@ -1943,7 +1951,7 @@
         <v>100</v>
       </c>
       <c r="H34" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I34" s="1">
         <v>7</v>
@@ -1956,7 +1964,7 @@
       <c r="C35" s="1">
         <v>35</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="4">
         <v>180035</v>
       </c>
       <c r="E35" s="1" t="s">
@@ -1982,7 +1990,7 @@
       <c r="C36" s="1">
         <v>36</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="4">
         <v>180036</v>
       </c>
       <c r="E36" s="1" t="s">

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="69">
   <si>
     <t>Id</t>
   </si>
@@ -185,6 +185,12 @@
     <t>神戒等级上限+1</t>
   </si>
   <si>
+    <t>传世契约</t>
+  </si>
+  <si>
+    <t>广告的传世劵收益+1</t>
+  </si>
+  <si>
     <t>极·卖身契</t>
   </si>
   <si>
@@ -222,6 +228,12 @@
   </si>
   <si>
     <t>魂环等级上限+2</t>
+  </si>
+  <si>
+    <t>极·传世契约</t>
+  </si>
+  <si>
+    <t>广告的传世劵收益+2</t>
   </si>
 </sst>
 </file>
@@ -1195,7 +1207,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J36"/>
+  <dimension ref="C3:J37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1830,6 +1842,32 @@
         <v>51</v>
       </c>
     </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C27" s="2">
+        <v>22</v>
+      </c>
+      <c r="D27" s="5">
+        <v>180022</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F27" s="2">
+        <v>22</v>
+      </c>
+      <c r="G27" s="2">
+        <v>1</v>
+      </c>
+      <c r="H27" s="2">
+        <v>4</v>
+      </c>
+      <c r="I27" s="2">
+        <v>6</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
     <row r="30" customHeight="1" spans="3:10">
       <c r="C30" s="1">
         <v>30</v>
@@ -1838,7 +1876,7 @@
         <v>180030</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F30" s="1">
         <v>30</v>
@@ -1853,7 +1891,7 @@
         <v>7</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:10">
@@ -1864,7 +1902,7 @@
         <v>180031</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -1890,7 +1928,7 @@
         <v>180032</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F32" s="1">
         <v>4</v>
@@ -1905,7 +1943,7 @@
         <v>7</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:10">
@@ -1916,7 +1954,7 @@
         <v>180033</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F33" s="1">
         <v>2</v>
@@ -1931,7 +1969,7 @@
         <v>7</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:10">
@@ -1942,7 +1980,7 @@
         <v>180034</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F34" s="1">
         <v>15</v>
@@ -1957,7 +1995,7 @@
         <v>7</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:10">
@@ -1968,7 +2006,7 @@
         <v>180035</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F35" s="1">
         <v>8</v>
@@ -1983,7 +2021,7 @@
         <v>7</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:10">
@@ -1994,7 +2032,7 @@
         <v>180036</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F36" s="1">
         <v>10</v>
@@ -2009,7 +2047,33 @@
         <v>7</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:10">
+      <c r="C37" s="1">
+        <v>37</v>
+      </c>
+      <c r="D37" s="4">
+        <v>180037</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F37" s="1">
+        <v>22</v>
+      </c>
+      <c r="G37" s="1">
+        <v>2</v>
+      </c>
+      <c r="H37" s="1">
+        <v>4</v>
+      </c>
+      <c r="I37" s="1">
+        <v>7</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -1807,7 +1807,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="2">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="I25" s="2">
         <v>6</v>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="73">
   <si>
     <t>Id</t>
   </si>
@@ -234,6 +234,18 @@
   </si>
   <si>
     <t>广告的传世劵收益+2</t>
+  </si>
+  <si>
+    <t>极·万界图</t>
+  </si>
+  <si>
+    <t>所有图鉴上限提高100%</t>
+  </si>
+  <si>
+    <t>极·金蛟剪</t>
+  </si>
+  <si>
+    <t>时装等级上限5%</t>
   </si>
 </sst>
 </file>
@@ -1207,7 +1219,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J37"/>
+  <dimension ref="C3:J39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -2076,6 +2088,58 @@
         <v>68</v>
       </c>
     </row>
+    <row r="38" customHeight="1" spans="3:10">
+      <c r="C38" s="1">
+        <v>38</v>
+      </c>
+      <c r="D38" s="4">
+        <v>180038</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F38" s="2">
+        <v>6</v>
+      </c>
+      <c r="G38" s="1">
+        <v>100</v>
+      </c>
+      <c r="H38" s="1">
+        <v>40</v>
+      </c>
+      <c r="I38" s="1">
+        <v>7</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:10">
+      <c r="C39" s="1">
+        <v>39</v>
+      </c>
+      <c r="D39" s="4">
+        <v>180039</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F39" s="1">
+        <v>39</v>
+      </c>
+      <c r="G39" s="1">
+        <v>5</v>
+      </c>
+      <c r="H39" s="1">
+        <v>10</v>
+      </c>
+      <c r="I39" s="1">
+        <v>7</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -1455,7 +1455,7 @@
         <v>10</v>
       </c>
       <c r="H11" s="2">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="I11" s="2">
         <v>6</v>
@@ -1637,7 +1637,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="2">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="I18" s="2">
         <v>6</v>
@@ -1663,7 +1663,7 @@
         <v>10</v>
       </c>
       <c r="H19" s="2">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I19" s="2">
         <v>6</v>
@@ -1689,7 +1689,7 @@
         <v>10</v>
       </c>
       <c r="H20" s="2">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I20" s="2">
         <v>6</v>
@@ -1741,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="2">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="I22" s="2">
         <v>6</v>
@@ -1767,7 +1767,7 @@
         <v>1</v>
       </c>
       <c r="H23" s="2">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="I23" s="2">
         <v>6</v>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -1455,7 +1455,7 @@
         <v>10</v>
       </c>
       <c r="H11" s="2">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="I11" s="2">
         <v>6</v>
@@ -1611,7 +1611,7 @@
         <v>5</v>
       </c>
       <c r="H17" s="2">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="I17" s="2">
         <v>6</v>
@@ -1637,7 +1637,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="2">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="I18" s="2">
         <v>6</v>
@@ -1663,7 +1663,7 @@
         <v>10</v>
       </c>
       <c r="H19" s="2">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="I19" s="2">
         <v>6</v>
@@ -1689,7 +1689,7 @@
         <v>10</v>
       </c>
       <c r="H20" s="2">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="I20" s="2">
         <v>6</v>
@@ -1741,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="2">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I22" s="2">
         <v>6</v>
@@ -1767,7 +1767,7 @@
         <v>1</v>
       </c>
       <c r="H23" s="2">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="I23" s="2">
         <v>6</v>
@@ -1897,7 +1897,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="1">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I30" s="1">
         <v>7</v>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -1223,10 +1223,10 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="6" width="12.625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.25" style="1" customWidth="1"/>
-    <col min="8" max="9" width="11.125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="24.875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="12.6283185840708" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.2477876106195" style="1" customWidth="1"/>
+    <col min="8" max="9" width="11.1238938053097" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24.8761061946903" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -2131,7 +2131,7 @@
         <v>5</v>
       </c>
       <c r="H39" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I39" s="1">
         <v>7</v>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -239,13 +239,13 @@
     <t>极·万界图</t>
   </si>
   <si>
-    <t>所有图鉴上限提高100%</t>
+    <t>所有图鉴基础上限提高10级</t>
   </si>
   <si>
     <t>极·金蛟剪</t>
   </si>
   <si>
-    <t>时装等级上限5%</t>
+    <t>时装等级上限10%</t>
   </si>
 </sst>
 </file>
@@ -2099,10 +2099,10 @@
         <v>69</v>
       </c>
       <c r="F38" s="2">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="G38" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H38" s="1">
         <v>40</v>
@@ -2128,7 +2128,7 @@
         <v>39</v>
       </c>
       <c r="G39" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H39" s="1">
         <v>20</v>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -212,19 +212,19 @@
     <t>广告的BOSS劵收益+2</t>
   </si>
   <si>
-    <t>极.财富契约</t>
+    <t>极·财富契约</t>
   </si>
   <si>
     <t>广告的金币经验收益+100%，每1个额外+1经验丹</t>
   </si>
   <si>
-    <t>极.魔法书</t>
+    <t>极·魔法书</t>
   </si>
   <si>
     <t>所有技能上限提高15%</t>
   </si>
   <si>
-    <t>极.无限之魂</t>
+    <t>极·无限之魂</t>
   </si>
   <si>
     <t>魂环等级上限+2</t>
@@ -239,7 +239,7 @@
     <t>极·万界图</t>
   </si>
   <si>
-    <t>所有图鉴基础上限提高10级</t>
+    <t>所有图鉴基础上限提高1级</t>
   </si>
   <si>
     <t>极·金蛟剪</t>
@@ -2102,7 +2102,7 @@
         <v>40</v>
       </c>
       <c r="G38" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H38" s="1">
         <v>40</v>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -1819,7 +1819,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="2">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="I25" s="2">
         <v>6</v>
@@ -1845,7 +1845,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="2">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="I26" s="2">
         <v>6</v>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -1223,10 +1223,10 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="6" width="12.6283185840708" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.2477876106195" style="1" customWidth="1"/>
-    <col min="8" max="9" width="11.1238938053097" style="1" customWidth="1"/>
-    <col min="10" max="10" width="24.8761061946903" style="1" customWidth="1"/>
+    <col min="5" max="6" width="12.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.25" style="1" customWidth="1"/>
+    <col min="8" max="9" width="11.125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24.875" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1455,7 +1455,7 @@
         <v>10</v>
       </c>
       <c r="H11" s="2">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="I11" s="2">
         <v>6</v>
@@ -1585,7 +1585,7 @@
         <v>1000</v>
       </c>
       <c r="H16" s="2">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I16" s="2">
         <v>6</v>
@@ -1637,7 +1637,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="2">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="I18" s="2">
         <v>6</v>
@@ -1663,7 +1663,7 @@
         <v>10</v>
       </c>
       <c r="H19" s="2">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="I19" s="2">
         <v>6</v>
@@ -1689,7 +1689,7 @@
         <v>10</v>
       </c>
       <c r="H20" s="2">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="I20" s="2">
         <v>6</v>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -1897,7 +1897,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="1">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I30" s="1">
         <v>7</v>
@@ -2131,7 +2131,7 @@
         <v>10</v>
       </c>
       <c r="H39" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I39" s="1">
         <v>7</v>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -1585,7 +1585,7 @@
         <v>1000</v>
       </c>
       <c r="H16" s="2">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="I16" s="2">
         <v>6</v>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -1637,7 +1637,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="2">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="I18" s="2">
         <v>6</v>
@@ -1819,7 +1819,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="2">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="I25" s="2">
         <v>6</v>
@@ -1845,7 +1845,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="2">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="I26" s="2">
         <v>6</v>
@@ -2131,7 +2131,7 @@
         <v>10</v>
       </c>
       <c r="H39" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I39" s="1">
         <v>7</v>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="79">
   <si>
     <t>Id</t>
   </si>
@@ -246,6 +246,24 @@
   </si>
   <si>
     <t>时装等级上限10%</t>
+  </si>
+  <si>
+    <t>极·炼体证明</t>
+  </si>
+  <si>
+    <t>炼体秘境的产出提高5%</t>
+  </si>
+  <si>
+    <t>极·炼气证明</t>
+  </si>
+  <si>
+    <t>炼气秘境的产出提高5%</t>
+  </si>
+  <si>
+    <t>极·炼神证明</t>
+  </si>
+  <si>
+    <t>炼神秘境的产出提高5%</t>
   </si>
 </sst>
 </file>
@@ -1219,7 +1237,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J39"/>
+  <dimension ref="C3:J42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -2053,7 +2071,7 @@
         <v>2</v>
       </c>
       <c r="H36" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I36" s="1">
         <v>7</v>
@@ -2099,7 +2117,7 @@
         <v>69</v>
       </c>
       <c r="F38" s="2">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G38" s="1">
         <v>1</v>
@@ -2138,6 +2156,84 @@
       </c>
       <c r="J39" s="2" t="s">
         <v>72</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:10">
+      <c r="C40" s="1">
+        <v>40</v>
+      </c>
+      <c r="D40" s="4">
+        <v>180040</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F40" s="1">
+        <v>40</v>
+      </c>
+      <c r="G40" s="1">
+        <v>5</v>
+      </c>
+      <c r="H40" s="1">
+        <v>20</v>
+      </c>
+      <c r="I40" s="1">
+        <v>7</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:10">
+      <c r="C41" s="1">
+        <v>41</v>
+      </c>
+      <c r="D41" s="4">
+        <v>180041</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F41" s="1">
+        <v>41</v>
+      </c>
+      <c r="G41" s="1">
+        <v>5</v>
+      </c>
+      <c r="H41" s="1">
+        <v>20</v>
+      </c>
+      <c r="I41" s="1">
+        <v>7</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:10">
+      <c r="C42" s="1">
+        <v>42</v>
+      </c>
+      <c r="D42" s="4">
+        <v>180042</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F42" s="1">
+        <v>42</v>
+      </c>
+      <c r="G42" s="1">
+        <v>5</v>
+      </c>
+      <c r="H42" s="1">
+        <v>20</v>
+      </c>
+      <c r="I42" s="1">
+        <v>7</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -1837,7 +1837,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="2">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="I25" s="2">
         <v>6</v>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -1759,7 +1759,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="2">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I22" s="2">
         <v>6</v>
@@ -1785,7 +1785,7 @@
         <v>1</v>
       </c>
       <c r="H23" s="2">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I23" s="2">
         <v>6</v>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -1655,7 +1655,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="2">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="I18" s="2">
         <v>6</v>
@@ -1681,7 +1681,7 @@
         <v>10</v>
       </c>
       <c r="H19" s="2">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="I19" s="2">
         <v>6</v>
@@ -1707,7 +1707,7 @@
         <v>10</v>
       </c>
       <c r="H20" s="2">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="I20" s="2">
         <v>6</v>
@@ -2019,7 +2019,7 @@
         <v>100</v>
       </c>
       <c r="H34" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I34" s="1">
         <v>7</v>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -1603,7 +1603,7 @@
         <v>1000</v>
       </c>
       <c r="H16" s="2">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="I16" s="2">
         <v>6</v>
@@ -1655,7 +1655,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="2">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="I18" s="2">
         <v>6</v>
@@ -1707,7 +1707,7 @@
         <v>10</v>
       </c>
       <c r="H20" s="2">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="I20" s="2">
         <v>6</v>
@@ -1837,7 +1837,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="2">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="I25" s="2">
         <v>6</v>
@@ -1863,7 +1863,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="2">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="I26" s="2">
         <v>6</v>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -1915,7 +1915,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="I30" s="1">
         <v>7</v>
@@ -2019,7 +2019,7 @@
         <v>100</v>
       </c>
       <c r="H34" s="1">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="I34" s="1">
         <v>7</v>
@@ -2123,7 +2123,7 @@
         <v>1</v>
       </c>
       <c r="H38" s="1">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="I38" s="1">
         <v>7</v>
@@ -2149,7 +2149,7 @@
         <v>10</v>
       </c>
       <c r="H39" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I39" s="1">
         <v>7</v>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -2019,7 +2019,7 @@
         <v>100</v>
       </c>
       <c r="H34" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="I34" s="1">
         <v>7</v>
@@ -2123,7 +2123,7 @@
         <v>1</v>
       </c>
       <c r="H38" s="1">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="I38" s="1">
         <v>7</v>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -1603,7 +1603,7 @@
         <v>1000</v>
       </c>
       <c r="H16" s="2">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="I16" s="2">
         <v>6</v>
@@ -1655,7 +1655,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="2">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="I18" s="2">
         <v>6</v>
@@ -1707,7 +1707,7 @@
         <v>10</v>
       </c>
       <c r="H20" s="2">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="I20" s="2">
         <v>6</v>
@@ -1759,7 +1759,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="2">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="I22" s="2">
         <v>6</v>
@@ -1785,7 +1785,7 @@
         <v>1</v>
       </c>
       <c r="H23" s="2">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="I23" s="2">
         <v>6</v>
@@ -1837,7 +1837,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="2">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="I25" s="2">
         <v>6</v>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -1915,7 +1915,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="1">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="I30" s="1">
         <v>7</v>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -1343,7 +1343,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I6" s="1">
         <v>6</v>
@@ -1369,7 +1369,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I7" s="1">
         <v>6</v>
@@ -1421,7 +1421,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I9" s="1">
         <v>6</v>
@@ -1447,7 +1447,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I10" s="1">
         <v>6</v>
@@ -1473,7 +1473,7 @@
         <v>10</v>
       </c>
       <c r="H11" s="2">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="I11" s="2">
         <v>6</v>
@@ -1525,7 +1525,7 @@
         <v>10</v>
       </c>
       <c r="H13" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I13" s="1">
         <v>6</v>
@@ -1577,7 +1577,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I15" s="1">
         <v>6</v>
@@ -1603,7 +1603,7 @@
         <v>1000</v>
       </c>
       <c r="H16" s="2">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I16" s="2">
         <v>6</v>
@@ -1629,7 +1629,7 @@
         <v>5</v>
       </c>
       <c r="H17" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I17" s="2">
         <v>6</v>
@@ -1655,7 +1655,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="2">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="I18" s="2">
         <v>6</v>
@@ -1681,7 +1681,7 @@
         <v>10</v>
       </c>
       <c r="H19" s="2">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="I19" s="2">
         <v>6</v>
@@ -1707,7 +1707,7 @@
         <v>10</v>
       </c>
       <c r="H20" s="2">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="I20" s="2">
         <v>6</v>
@@ -1759,7 +1759,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="2">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="I22" s="2">
         <v>6</v>
@@ -1785,7 +1785,7 @@
         <v>1</v>
       </c>
       <c r="H23" s="2">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="I23" s="2">
         <v>6</v>
@@ -1837,7 +1837,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="2">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="I25" s="2">
         <v>6</v>
@@ -1863,7 +1863,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="2">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="I26" s="2">
         <v>6</v>
@@ -1889,7 +1889,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I27" s="2">
         <v>6</v>
@@ -1967,7 +1967,7 @@
         <v>3</v>
       </c>
       <c r="H32" s="1">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I32" s="1">
         <v>7</v>
@@ -1993,7 +1993,7 @@
         <v>2</v>
       </c>
       <c r="H33" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I33" s="1">
         <v>7</v>
@@ -2019,7 +2019,7 @@
         <v>100</v>
       </c>
       <c r="H34" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I34" s="1">
         <v>7</v>
@@ -2045,7 +2045,7 @@
         <v>15</v>
       </c>
       <c r="H35" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I35" s="1">
         <v>7</v>
@@ -2071,7 +2071,7 @@
         <v>2</v>
       </c>
       <c r="H36" s="1">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I36" s="1">
         <v>7</v>
@@ -2097,7 +2097,7 @@
         <v>2</v>
       </c>
       <c r="H37" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I37" s="1">
         <v>7</v>
@@ -2123,7 +2123,7 @@
         <v>1</v>
       </c>
       <c r="H38" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I38" s="1">
         <v>7</v>
@@ -2149,7 +2149,7 @@
         <v>10</v>
       </c>
       <c r="H39" s="1">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="I39" s="1">
         <v>7</v>
@@ -2175,7 +2175,7 @@
         <v>5</v>
       </c>
       <c r="H40" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I40" s="1">
         <v>7</v>
@@ -2201,7 +2201,7 @@
         <v>5</v>
       </c>
       <c r="H41" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I41" s="1">
         <v>7</v>
@@ -2227,7 +2227,7 @@
         <v>5</v>
       </c>
       <c r="H42" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I42" s="1">
         <v>7</v>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="81">
   <si>
     <t>Id</t>
   </si>
@@ -264,6 +264,12 @@
   </si>
   <si>
     <t>炼神秘境的产出提高5%</t>
+  </si>
+  <si>
+    <t>极·炼魂证明</t>
+  </si>
+  <si>
+    <t>炼魂秘境的产出提高5%</t>
   </si>
 </sst>
 </file>
@@ -1237,7 +1243,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J42"/>
+  <dimension ref="C3:J43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -2236,6 +2242,32 @@
         <v>78</v>
       </c>
     </row>
+    <row r="43" customHeight="1" spans="3:10">
+      <c r="C43" s="1">
+        <v>43</v>
+      </c>
+      <c r="D43" s="4">
+        <v>180043</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F43" s="1">
+        <v>43</v>
+      </c>
+      <c r="G43" s="1">
+        <v>5</v>
+      </c>
+      <c r="H43" s="1">
+        <v>40</v>
+      </c>
+      <c r="I43" s="1">
+        <v>7</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="85">
   <si>
     <t>Id</t>
   </si>
@@ -270,6 +275,18 @@
   </si>
   <si>
     <t>炼魂秘境的产出提高5%</t>
+  </si>
+  <si>
+    <t>极戒之源</t>
+  </si>
+  <si>
+    <t>极戒等级上限+1</t>
+  </si>
+  <si>
+    <t>道戒之源</t>
+  </si>
+  <si>
+    <t>道戒等级上限+1</t>
   </si>
 </sst>
 </file>
@@ -915,7 +932,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -924,6 +941,8 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1243,7 +1262,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J43"/>
+  <dimension ref="C3:J45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -2119,22 +2138,22 @@
       <c r="D38" s="4">
         <v>180038</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="7">
         <v>23</v>
       </c>
-      <c r="G38" s="1">
-        <v>1</v>
-      </c>
-      <c r="H38" s="1">
+      <c r="G38" s="6">
+        <v>1</v>
+      </c>
+      <c r="H38" s="6">
         <v>60</v>
       </c>
-      <c r="I38" s="1">
+      <c r="I38" s="6">
         <v>7</v>
       </c>
-      <c r="J38" s="2" t="s">
+      <c r="J38" s="7" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2145,22 +2164,22 @@
       <c r="D39" s="4">
         <v>180039</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39" s="6">
         <v>39</v>
       </c>
-      <c r="G39" s="1">
+      <c r="G39" s="6">
         <v>10</v>
       </c>
-      <c r="H39" s="1">
+      <c r="H39" s="6">
         <v>90</v>
       </c>
-      <c r="I39" s="1">
+      <c r="I39" s="6">
         <v>7</v>
       </c>
-      <c r="J39" s="2" t="s">
+      <c r="J39" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2171,22 +2190,22 @@
       <c r="D40" s="4">
         <v>180040</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F40" s="6">
         <v>40</v>
       </c>
-      <c r="G40" s="1">
+      <c r="G40" s="6">
         <v>5</v>
       </c>
-      <c r="H40" s="1">
+      <c r="H40" s="6">
         <v>40</v>
       </c>
-      <c r="I40" s="1">
+      <c r="I40" s="6">
         <v>7</v>
       </c>
-      <c r="J40" s="2" t="s">
+      <c r="J40" s="7" t="s">
         <v>74</v>
       </c>
     </row>
@@ -2197,22 +2216,22 @@
       <c r="D41" s="4">
         <v>180041</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F41" s="6">
         <v>41</v>
       </c>
-      <c r="G41" s="1">
+      <c r="G41" s="6">
         <v>5</v>
       </c>
-      <c r="H41" s="1">
+      <c r="H41" s="6">
         <v>40</v>
       </c>
-      <c r="I41" s="1">
+      <c r="I41" s="6">
         <v>7</v>
       </c>
-      <c r="J41" s="2" t="s">
+      <c r="J41" s="7" t="s">
         <v>76</v>
       </c>
     </row>
@@ -2223,22 +2242,22 @@
       <c r="D42" s="4">
         <v>180042</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F42" s="6">
         <v>42</v>
       </c>
-      <c r="G42" s="1">
+      <c r="G42" s="6">
         <v>5</v>
       </c>
-      <c r="H42" s="1">
+      <c r="H42" s="6">
         <v>40</v>
       </c>
-      <c r="I42" s="1">
+      <c r="I42" s="6">
         <v>7</v>
       </c>
-      <c r="J42" s="2" t="s">
+      <c r="J42" s="7" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2249,23 +2268,75 @@
       <c r="D43" s="4">
         <v>180043</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F43" s="6">
         <v>43</v>
       </c>
-      <c r="G43" s="1">
+      <c r="G43" s="6">
         <v>5</v>
       </c>
-      <c r="H43" s="1">
+      <c r="H43" s="6">
         <v>40</v>
       </c>
-      <c r="I43" s="1">
+      <c r="I43" s="6">
         <v>7</v>
       </c>
-      <c r="J43" s="2" t="s">
+      <c r="J43" s="7" t="s">
         <v>80</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:10">
+      <c r="C44" s="1">
+        <v>44</v>
+      </c>
+      <c r="D44" s="4">
+        <v>180044</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F44" s="7">
+        <v>44</v>
+      </c>
+      <c r="G44" s="7">
+        <v>1</v>
+      </c>
+      <c r="H44" s="7">
+        <v>20</v>
+      </c>
+      <c r="I44" s="6">
+        <v>7</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:10">
+      <c r="C45" s="1">
+        <v>45</v>
+      </c>
+      <c r="D45" s="4">
+        <v>180045</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F45" s="7">
+        <v>45</v>
+      </c>
+      <c r="G45" s="7">
+        <v>1</v>
+      </c>
+      <c r="H45" s="7">
+        <v>20</v>
+      </c>
+      <c r="I45" s="6">
+        <v>7</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -932,7 +932,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -941,7 +941,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1602,7 +1601,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="1">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="I15" s="1">
         <v>6</v>
@@ -2096,7 +2095,7 @@
         <v>2</v>
       </c>
       <c r="H36" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I36" s="1">
         <v>7</v>
@@ -2141,7 +2140,7 @@
       <c r="E38" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="F38" s="7">
+      <c r="F38" s="6">
         <v>23</v>
       </c>
       <c r="G38" s="6">
@@ -2153,7 +2152,7 @@
       <c r="I38" s="6">
         <v>7</v>
       </c>
-      <c r="J38" s="7" t="s">
+      <c r="J38" s="6" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2179,7 +2178,7 @@
       <c r="I39" s="6">
         <v>7</v>
       </c>
-      <c r="J39" s="7" t="s">
+      <c r="J39" s="6" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2205,7 +2204,7 @@
       <c r="I40" s="6">
         <v>7</v>
       </c>
-      <c r="J40" s="7" t="s">
+      <c r="J40" s="6" t="s">
         <v>74</v>
       </c>
     </row>
@@ -2231,7 +2230,7 @@
       <c r="I41" s="6">
         <v>7</v>
       </c>
-      <c r="J41" s="7" t="s">
+      <c r="J41" s="6" t="s">
         <v>76</v>
       </c>
     </row>
@@ -2257,7 +2256,7 @@
       <c r="I42" s="6">
         <v>7</v>
       </c>
-      <c r="J42" s="7" t="s">
+      <c r="J42" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2283,7 +2282,7 @@
       <c r="I43" s="6">
         <v>7</v>
       </c>
-      <c r="J43" s="7" t="s">
+      <c r="J43" s="6" t="s">
         <v>80</v>
       </c>
     </row>
@@ -2294,22 +2293,22 @@
       <c r="D44" s="4">
         <v>180044</v>
       </c>
-      <c r="E44" s="7" t="s">
+      <c r="E44" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F44" s="7">
+      <c r="F44" s="6">
         <v>44</v>
       </c>
-      <c r="G44" s="7">
-        <v>1</v>
-      </c>
-      <c r="H44" s="7">
+      <c r="G44" s="6">
+        <v>1</v>
+      </c>
+      <c r="H44" s="6">
         <v>20</v>
       </c>
       <c r="I44" s="6">
         <v>7</v>
       </c>
-      <c r="J44" s="7" t="s">
+      <c r="J44" s="6" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2320,22 +2319,22 @@
       <c r="D45" s="4">
         <v>180045</v>
       </c>
-      <c r="E45" s="7" t="s">
+      <c r="E45" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="F45" s="7">
+      <c r="F45" s="6">
         <v>45</v>
       </c>
-      <c r="G45" s="7">
-        <v>1</v>
-      </c>
-      <c r="H45" s="7">
+      <c r="G45" s="6">
+        <v>1</v>
+      </c>
+      <c r="H45" s="6">
         <v>20</v>
       </c>
       <c r="I45" s="6">
         <v>7</v>
       </c>
-      <c r="J45" s="7" t="s">
+      <c r="J45" s="6" t="s">
         <v>84</v>
       </c>
     </row>
